--- a/artfynd/A 43956-2025 artfynd.xlsx
+++ b/artfynd/A 43956-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>128467838</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128467857</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128467737</v>
       </c>
       <c r="B5" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128467724</v>
       </c>
       <c r="B6" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128467886</v>
       </c>
       <c r="B7" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128467876</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43956-2025 artfynd.xlsx
+++ b/artfynd/A 43956-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>128467838</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128467857</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128467737</v>
       </c>
       <c r="B5" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128467724</v>
       </c>
       <c r="B6" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128467886</v>
       </c>
       <c r="B7" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128467876</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43956-2025 artfynd.xlsx
+++ b/artfynd/A 43956-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>128467838</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128467857</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128467737</v>
       </c>
       <c r="B5" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128467724</v>
       </c>
       <c r="B6" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128467886</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128467876</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43956-2025 artfynd.xlsx
+++ b/artfynd/A 43956-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>128467838</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128467857</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128467737</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128467724</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128467886</v>
       </c>
       <c r="B7" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128467876</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43956-2025 artfynd.xlsx
+++ b/artfynd/A 43956-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>128467838</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128467857</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128467737</v>
       </c>
       <c r="B5" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128467724</v>
       </c>
       <c r="B6" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128467886</v>
       </c>
       <c r="B7" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128467876</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43956-2025 artfynd.xlsx
+++ b/artfynd/A 43956-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>128467838</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128467857</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128467737</v>
       </c>
       <c r="B5" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128467724</v>
       </c>
       <c r="B6" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128467886</v>
       </c>
       <c r="B7" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128467876</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43956-2025 artfynd.xlsx
+++ b/artfynd/A 43956-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>128467838</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128467857</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128467737</v>
       </c>
       <c r="B5" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128467724</v>
       </c>
       <c r="B6" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>128467886</v>
       </c>
       <c r="B7" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>128467876</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43956-2025 artfynd.xlsx
+++ b/artfynd/A 43956-2025 artfynd.xlsx
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78491711</v>
+        <v>128467838</v>
       </c>
       <c r="B2" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>92, Norrstrand, Ås lm</t>
+          <t>Kyrkskogen Åsele, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616968.5177499127</v>
+        <v>617257</v>
       </c>
       <c r="R2" t="n">
-        <v>7118689.382994503</v>
+        <v>7118631</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,32 +757,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Kristofer Lindblom</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Kristofer Lindblom</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128467838</v>
+        <v>128467857</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617257</v>
+        <v>617264</v>
       </c>
       <c r="R3" t="n">
-        <v>7118631</v>
+        <v>7118624</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,14 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128467857</v>
+        <v>128467876</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -928,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617264</v>
+        <v>617088</v>
       </c>
       <c r="R4" t="n">
-        <v>7118624</v>
+        <v>7118551</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128467737</v>
+        <v>128467724</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617236</v>
+        <v>617258</v>
       </c>
       <c r="R5" t="n">
-        <v>7118696</v>
+        <v>7118709</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128467724</v>
+        <v>128467737</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617258</v>
+        <v>617236</v>
       </c>
       <c r="R6" t="n">
-        <v>7118709</v>
+        <v>7118696</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1183,7 @@
         <v>128467886</v>
       </c>
       <c r="B7" t="n">
-        <v>80163</v>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,48 +1281,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128467876</v>
+        <v>78491711</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>97989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kyrkskogen Åsele, Ås lm</t>
+          <t>92, Norrstrand, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>617088</v>
+        <v>616969</v>
       </c>
       <c r="R8" t="n">
-        <v>7118551</v>
+        <v>7118689</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,12 +1348,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1376,19 +1362,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristofer Lindblom</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristofer Lindblom</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 43956-2025 artfynd.xlsx
+++ b/artfynd/A 43956-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128467838</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128467857</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128467876</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128467724</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128467737</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128467886</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,8 +1412,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78491711</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>